--- a/artfynd/A 53634-2021 artfynd.xlsx
+++ b/artfynd/A 53634-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97643896</v>
+        <v>97643822</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497108.0748773717</v>
+        <v>497157</v>
       </c>
       <c r="R2" t="n">
-        <v>6802856.328475502</v>
+        <v>6802777</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +743,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97643875</v>
+        <v>97643900</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497205.5474775246</v>
+        <v>497126</v>
       </c>
       <c r="R3" t="n">
-        <v>6802806.368773252</v>
+        <v>6802753</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +840,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97643900</v>
+        <v>97643877</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497125.2832204383</v>
+        <v>497150</v>
       </c>
       <c r="R4" t="n">
-        <v>6802753.675145656</v>
+        <v>6802915</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,19 +937,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97643852</v>
+        <v>97643850</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497132.0281214747</v>
+        <v>497186</v>
       </c>
       <c r="R5" t="n">
-        <v>6802777.65096934</v>
+        <v>6802790</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1034,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97643898</v>
+        <v>97643894</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497094.1309423185</v>
+        <v>497076</v>
       </c>
       <c r="R6" t="n">
-        <v>6802840.033106218</v>
+        <v>6802879</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1200,19 +1131,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97643850</v>
+        <v>97643898</v>
       </c>
       <c r="B7" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497185.839401867</v>
+        <v>497094</v>
       </c>
       <c r="R7" t="n">
-        <v>6802790.077424451</v>
+        <v>6802840</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,19 +1228,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97643825</v>
+        <v>97643886</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497204.5986550352</v>
+        <v>497139</v>
       </c>
       <c r="R8" t="n">
-        <v>6802821.237778109</v>
+        <v>6802929</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1424,19 +1325,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97643813</v>
+        <v>97643834</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497105.2539815648</v>
+        <v>497148</v>
       </c>
       <c r="R9" t="n">
-        <v>6802930.190746767</v>
+        <v>6802926</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1536,19 +1422,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97643862</v>
+        <v>97643871</v>
       </c>
       <c r="B10" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497211.3294714994</v>
+        <v>497124</v>
       </c>
       <c r="R10" t="n">
-        <v>6802828.426684384</v>
+        <v>6802899</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1648,19 +1519,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97643847</v>
+        <v>97643875</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497095.0449659828</v>
+        <v>497206</v>
       </c>
       <c r="R11" t="n">
-        <v>6802783.916677721</v>
+        <v>6802807</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1760,19 +1616,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,54 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97643815</v>
+        <v>97643845</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497117.6463827597</v>
+        <v>497117</v>
       </c>
       <c r="R12" t="n">
-        <v>6802813.154942275</v>
+        <v>6802818</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1876,19 +1713,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97643811</v>
+        <v>97643847</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497127.2208882539</v>
+        <v>497095</v>
       </c>
       <c r="R13" t="n">
-        <v>6802773.33828722</v>
+        <v>6802784</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1988,19 +1810,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97643871</v>
+        <v>97643858</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2067,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497123.4818789206</v>
+        <v>497116</v>
       </c>
       <c r="R14" t="n">
-        <v>6802899.480831095</v>
+        <v>6802812</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2100,19 +1907,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,54 +1936,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97643890</v>
+        <v>97643880</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497114.7610322455</v>
+        <v>497112</v>
       </c>
       <c r="R15" t="n">
-        <v>6802809.320356285</v>
+        <v>6802757</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,19 +2004,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97643860</v>
+        <v>97643882</v>
       </c>
       <c r="B16" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497205.5547721307</v>
+        <v>497127</v>
       </c>
       <c r="R16" t="n">
-        <v>6802815.481570352</v>
+        <v>6802774</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,19 +2101,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,50 +2130,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97643882</v>
+        <v>97643815</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497127.2208882539</v>
+        <v>497117</v>
       </c>
       <c r="R17" t="n">
-        <v>6802773.33828722</v>
+        <v>6802813</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,19 +2202,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,50 +2231,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97643822</v>
+        <v>97643884</v>
       </c>
       <c r="B18" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497157.0064817477</v>
+        <v>497090</v>
       </c>
       <c r="R18" t="n">
-        <v>6802776.671286538</v>
+        <v>6802845</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,19 +2303,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,50 +2332,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97643858</v>
+        <v>97643890</v>
       </c>
       <c r="B19" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497116.6848640497</v>
+        <v>497115</v>
       </c>
       <c r="R19" t="n">
-        <v>6802812.196494315</v>
+        <v>6802810</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,19 +2404,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,50 +2433,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97643845</v>
+        <v>97643896</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ivarsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497117.6507387998</v>
+        <v>497108</v>
       </c>
       <c r="R20" t="n">
-        <v>6802818.430764874</v>
+        <v>6802856</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,19 +2505,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,37 +2534,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97643880</v>
+        <v>97643811</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497112.3163664356</v>
+        <v>497127</v>
       </c>
       <c r="R21" t="n">
-        <v>6802757.522877823</v>
+        <v>6802774</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,19 +2602,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,15 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97643867</v>
+        <v>97643813</v>
       </c>
       <c r="B22" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497109.4365239705</v>
+        <v>497105</v>
       </c>
       <c r="R22" t="n">
-        <v>6802760.403031224</v>
+        <v>6802930</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,19 +2699,9 @@
           <t>2021-11-25</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-11-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,6 +2725,588 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97643825</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>497204</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6802821</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>97643843</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497092</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6802844</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>97643852</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>497132</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6802777</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>97643860</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>497205</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6802815</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>97643862</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497212</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6802829</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>97643867</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ivarsån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497109</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6802760</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53634-2021 artfynd.xlsx
+++ b/artfynd/A 53634-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643877</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643850</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643886</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643871</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643875</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643845</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643847</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643858</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643880</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643882</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643815</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643884</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643890</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2531,6 +2626,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643896</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2628,6 +2728,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643811</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2725,6 +2830,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643813</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643825</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2919,6 +3034,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643843</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3016,6 +3136,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643852</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3113,6 +3238,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643860</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3210,6 +3340,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643862</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3307,8 +3442,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97643867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>